--- a/rules/CORE-000109/negative/01/data/unit-test-CG0547-negative.xlsx
+++ b/rules/CORE-000109/negative/01/data/unit-test-CG0547-negative.xlsx
@@ -1,166 +1,293 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Jozef"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="0" windowHeight="0" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sm.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Library" sheetId="1" r:id="rId4"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId5"/>
+    <sheet name="Validation" sheetId="3" r:id="rId6"/>
+    <sheet name="sm.xpt" sheetId="4" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr/>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1776831042" val="1234" rev="124" rev64="64" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1776831042" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1776831042" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1776831042"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>DIAGNOSISS</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="10">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;€&quot;;\-#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;€&quot;;\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="49" formatCode="@"/>
+    <numFmt numFmtId="1" formatCode="0"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1776831042" ulstyle="none" kern="1">
+            <pm:latin face="Calibri" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1776831042" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <i val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1776831042" ulstyle="none" kern="1">
+            <pm:latin face="Calibri" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1776831042" ulstyle="none" kern="1">
+            <pm:latin face="Calibri" sz="220" lang="default" i="1"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" i="1"/>
+            <pm:ea face="SimSun" sz="220" lang="default" i="1"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
-        <bgColor rgb="00FFFFCC"/>
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1776831042" type="1" fgLvl="13" fgClr="00000000" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1776831042" type="1" fgLvl="100" fgClr="00FFFFCC" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1776831042" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1776831042" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1776831042"/>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="none">
+        <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="none">
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="none">
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="none">
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1776831042"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1776831042"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1776831042"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1776831042"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0"/>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:charStyles xmlns:pm="smNativeData" id="1776831042" count="1">
+        <pm:charStyle name="Normal" fontId="0" Id="1"/>
+      </pm:charStyles>
+      <pm:colors xmlns:pm="smNativeData" id="1776831042" count="1">
+        <pm:color name="Colour 24" rgb="FFFFCC"/>
+      </pm:colors>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -175,10 +302,10 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="EEECE1"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="1F497D"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -210,69 +337,11 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="SimSun"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -442,299 +511,542 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr>
+        <a:prstTxWarp prst="textNoShape">
+          <a:avLst/>
+        </a:prstTxWarp>
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr>
+          <a:defRPr/>
+        </a:defPPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15.40"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
+    <row r="1" spans="1:2">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t>Product</t>
+          </r>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t>Version</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>sdtmig</t>
+          </r>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>3-4</t>
+          </r>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1776831042" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.787500" right="0.787500" top="0.787500" bottom="0.787500" header="0.393750" footer="0.393750"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1776831042" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1776831042" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776831042" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776831042" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776831042" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15.40"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <r>
+            <t>Filename</t>
+          </r>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sm.xpt</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Subject Disease Milestones</t>
+          <r>
+            <t>Label</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>sm.xpt</t>
+          </r>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>Subject Disease Milestones</t>
+          </r>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1776831042" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.787500" right="0.787500" top="0.787500" bottom="0.787500" header="0.393750" footer="0.393750"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1776831042" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1776831042" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776831042" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776831042" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776831042" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15.40"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Error group</t>
+          <r>
+            <t>Error group</t>
+          </r>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sheet</t>
+          <r>
+            <t>Sheet</t>
+          </r>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Error level</t>
+          <r>
+            <t>Error level</t>
+          </r>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Row num</t>
+          <r>
+            <t>Row num</t>
+          </r>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <r>
+            <t>Variable</t>
+          </r>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Error value</t>
-        </is>
-      </c>
+          <r>
+            <t>Error value</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>sm.xpt</t>
+          </r>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>Record</t>
+          </r>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>SMSTDTC</t>
+          </r>
+        </is>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>sm.xpt</t>
+          </r>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>Record</t>
+          </r>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>SMSTDTC</t>
+          </r>
+        </is>
+      </c>
+      <c r="F3" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1776831042" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.787500" right="0.787500" top="0.787500" bottom="0.787500" header="0.393750" footer="0.393750"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1776831042" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1776831042" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776831042" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776831042" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776831042" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15.40"/>
+  <cols>
+    <col min="6" max="6" width="20.857143" customWidth="1"/>
+    <col min="7" max="7" width="14.428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>DOMAIN</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>SMSEQ</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>MIDS</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>MIDSTYPE</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>SMSTDTC</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>SMENDTC</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>SMSTDY</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>SMENDY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>STUDYID</t>
+          </r>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>DOMAIN</t>
+          </r>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>USUBJID</t>
+          </r>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>SMSEQ</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>MIDS</t>
+          </r>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>MIDSTYPE</t>
+          </r>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>SMSTDTC</t>
+          </r>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>SMENDTC</t>
+          </r>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>SMSTDY</t>
+          </r>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <t>SMENDY</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Study Identifier</t>
+          <r>
+            <t>Study Identifier</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Domain Abbreviation</t>
+          <r>
+            <t>Domain Abbreviation</t>
+          </r>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Unique Subject Identifier</t>
+          <r>
+            <t>Unique Subject Identifier</t>
+          </r>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Sequence Number</t>
+          <r>
+            <t>Sequence Number</t>
+          </r>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Disease Milestone Instance Name</t>
+          <r>
+            <t>Disease Milestone Instance Name</t>
+          </r>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Disease Milestone Type</t>
+          <r>
+            <t>Disease Milestone Type</t>
+          </r>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Start Date/Time of Milestone</t>
+          <r>
+            <t>Start Date/Time of Milestone</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>End Date/Time of Milestone</t>
+          <r>
+            <t>End Date/Time of Milestone</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Study Day of Start of Milestone</t>
+          <r>
+            <t>Study Day of Start of Milestone</t>
+          </r>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Study Day of End of Milestone</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <r>
+            <t>Study Day of End of Milestone</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Char</t>
+          <r>
+            <t>Char</t>
+          </r>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Char</t>
+          <r>
+            <t>Char</t>
+          </r>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Char</t>
+          <r>
+            <t>Char</t>
+          </r>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Num</t>
+          <r>
+            <t>Num</t>
+          </r>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Char</t>
+          <r>
+            <t>Char</t>
+          </r>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Char</t>
+          <r>
+            <t>Char</t>
+          </r>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Char</t>
+          <r>
+            <t>Char</t>
+          </r>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Char</t>
+          <r>
+            <t>Char</t>
+          </r>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Num</t>
+          <r>
+            <t>Num</t>
+          </r>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Num</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <r>
+            <t>Num</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="3" t="n">
         <v>50</v>
       </c>
@@ -766,170 +1078,274 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <r>
+            <t>XYZ</t>
+          </r>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SM</t>
+          <r>
+            <t>SM</t>
+          </r>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <r>
+            <t>001</t>
+          </r>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>1</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>DIAG</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>DIAGNOSIS</t>
-        </is>
-      </c>
+          <r>
+            <t>DIAG</t>
+          </r>
+        </is>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2005-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <r>
+            <t>2005-10</t>
+          </r>
+        </is>
+      </c>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <r>
+            <t>XYZ</t>
+          </r>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SM</t>
+          <r>
+            <t>SM</t>
+          </r>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <r>
+            <t>001</t>
+          </r>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>2</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>HYPO1</t>
+          <r>
+            <t>HYPO1</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>HYPOGLYCEMIC EVENT</t>
-        </is>
-      </c>
+          <r>
+            <t>HYPOGLYCEMIC EVENT</t>
+          </r>
+        </is>
+      </c>
+      <c r="G6" s="6"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>2013-09-01T11:00</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <r>
+            <t>2013-09-01T11:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>25</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <r>
+            <t>XYZ</t>
+          </r>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SM</t>
+          <r>
+            <t>SM</t>
+          </r>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
+          <r>
+            <t>001</t>
+          </r>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>3</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>HYPO2</t>
+          <r>
+            <t>HYPO2</t>
+          </r>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>HYPOGLYCEMIC EVENT</t>
+          <r>
+            <t>HYPOGLYCEMIC EVENT</t>
+          </r>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>2013-09-24T08:48</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2013-09-24T08:48</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <r>
+            <t>2013-09-24T08:48</t>
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>50</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <r>
+            <t>XYZ</t>
+          </r>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SM</t>
+          <r>
+            <t>SM</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>002</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <r>
+            <t>002</t>
+          </r>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>1</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>DIAG</t>
+          <r>
+            <t>DIAG</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>DIAGNOSIS</t>
+          <r>
+            <t>DIAGNOSIS</t>
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t>2010-05-15</t>
+          </r>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>2010-05-15</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>-1046</t>
+          <r>
+            <t>2010-05-15</t>
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t>-1046</t>
+          </r>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1776831042" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.787500" right="0.787500" top="0.787500" bottom="0.787500" header="0.393750" footer="0.393750"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1776831042" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1776831042" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776831042" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776831042" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776831042" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>